--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -713,17 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
